--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C2308F-C608-4C63-A03C-B6BF80BA5005}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AF583E-8F26-4221-9ADE-2F211C11E187}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3383,7 +3383,9 @@
       <c r="A34">
         <v>2</v>
       </c>
-      <c r="C34" s="19"/>
+      <c r="C34" s="19">
+        <v>46150</v>
+      </c>
       <c r="D34" s="20" t="s">
         <v>68</v>
       </c>
@@ -3399,18 +3401,21 @@
       </c>
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
-      <c r="K34" s="21"/>
+      <c r="K34" s="21">
+        <f>23976+10656+167832</f>
+        <v>202464</v>
+      </c>
       <c r="M34" s="21">
         <f t="shared" ref="M34:M53" si="8">O34*12</f>
-        <v>0</v>
+        <v>21692.571428571428</v>
       </c>
       <c r="N34" s="27">
         <f>K34-M34</f>
-        <v>0</v>
+        <v>180771.42857142858</v>
       </c>
       <c r="O34" s="33">
         <f t="shared" ref="O34:O53" si="9">K34/112</f>
-        <v>0</v>
+        <v>1807.7142857142858</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -4047,7 +4052,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>0</v>
+        <v>202464</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4055,15 +4060,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>0</v>
+        <v>21692.571428571428</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>0</v>
+        <v>180771.42857142858</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>0</v>
+        <v>1807.7142857142858</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AF583E-8F26-4221-9ADE-2F211C11E187}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A5C5D4-EDF0-4F24-B9FE-E415E53D2F8D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="88">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>AUGUST 2026</t>
+  </si>
+  <si>
+    <t>R02</t>
   </si>
 </sst>
 </file>
@@ -3422,7 +3425,9 @@
       <c r="A35">
         <v>3</v>
       </c>
-      <c r="C35" s="19"/>
+      <c r="C35" s="19">
+        <v>46211</v>
+      </c>
       <c r="D35" s="20" t="s">
         <v>68</v>
       </c>
@@ -3430,24 +3435,29 @@
       <c r="F35" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G35" s="37"/>
+      <c r="G35" s="37" t="s">
+        <v>87</v>
+      </c>
       <c r="H35" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I35" s="20"/>
       <c r="J35" s="20"/>
-      <c r="K35" s="21"/>
+      <c r="K35" s="21">
+        <f>8640+11988+7560+167832</f>
+        <v>196020</v>
+      </c>
       <c r="M35" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21002.142857142855</v>
       </c>
       <c r="N35" s="27">
         <f t="shared" ref="N35:N53" si="10">K35-M35</f>
-        <v>0</v>
+        <v>175017.85714285716</v>
       </c>
       <c r="O35" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1750.1785714285713</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -4052,7 +4062,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>202464</v>
+        <v>398484</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4060,15 +4070,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>21692.571428571428</v>
+        <v>42694.714285714283</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>180771.42857142858</v>
+        <v>355789.28571428574</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>1807.7142857142858</v>
+        <v>3557.8928571428569</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A5C5D4-EDF0-4F24-B9FE-E415E53D2F8D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8A9C7C-C94B-4D59-ABBD-FC6C1315308B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="89">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>R02</t>
+  </si>
+  <si>
+    <t>R03</t>
   </si>
 </sst>
 </file>
@@ -2423,7 +2426,9 @@
       <c r="B7" s="23">
         <v>1</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="19">
+        <v>46334</v>
+      </c>
       <c r="D7" s="20" t="s">
         <v>68</v>
       </c>
@@ -2431,27 +2436,35 @@
       <c r="F7" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="20"/>
+      <c r="G7" s="20">
+        <v>518900758</v>
+      </c>
       <c r="H7" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
+      <c r="I7" s="21">
+        <f>1318233</f>
+        <v>1318233</v>
+      </c>
+      <c r="J7" s="21">
+        <f>53845.98</f>
+        <v>53845.98</v>
+      </c>
       <c r="K7" s="21">
         <f>I7-J7</f>
-        <v>0</v>
+        <v>1264387.02</v>
       </c>
       <c r="M7" s="21">
         <f>O7*12</f>
-        <v>0</v>
+        <v>135470.03785714286</v>
       </c>
       <c r="N7" s="27">
         <f>K7-M7</f>
-        <v>0</v>
+        <v>1128916.9821428573</v>
       </c>
       <c r="O7" s="33">
         <f>K7/112</f>
-        <v>0</v>
+        <v>11289.169821428572</v>
       </c>
       <c r="P7" s="26"/>
       <c r="Q7" s="26"/>
@@ -3262,7 +3275,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>0</v>
+        <v>1264387.02</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3270,15 +3283,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>0</v>
+        <v>135470.03785714286</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>0</v>
+        <v>1128916.9821428573</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>0</v>
+        <v>11289.169821428572</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3464,7 +3477,9 @@
       <c r="A36">
         <v>4</v>
       </c>
-      <c r="C36" s="19"/>
+      <c r="C36" s="19">
+        <v>46334</v>
+      </c>
       <c r="D36" s="20" t="s">
         <v>68</v>
       </c>
@@ -3472,24 +3487,29 @@
       <c r="F36" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G36" s="37"/>
+      <c r="G36" s="37" t="s">
+        <v>88</v>
+      </c>
       <c r="H36" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I36" s="20"/>
       <c r="J36" s="20"/>
-      <c r="K36" s="21"/>
+      <c r="K36" s="21">
+        <f>35964+167832</f>
+        <v>203796</v>
+      </c>
       <c r="M36" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N36" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O36" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -4062,7 +4082,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>398484</v>
+        <v>602280</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4070,15 +4090,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>42694.714285714283</v>
+        <v>64530</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>355789.28571428574</v>
+        <v>537750</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>3557.8928571428569</v>
+        <v>5377.5</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8A9C7C-C94B-4D59-ABBD-FC6C1315308B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD115620-76C9-43AC-A518-7928CD15E53F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="92">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -300,6 +300,15 @@
   </si>
   <si>
     <t>R03</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>08/15/2026</t>
+  </si>
+  <si>
+    <t>R06</t>
   </si>
 </sst>
 </file>
@@ -2478,7 +2487,9 @@
         <f>B7+1</f>
         <v>2</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="D8" s="20" t="s">
         <v>68</v>
       </c>
@@ -2486,27 +2497,33 @@
       <c r="F8" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="20">
+        <v>518912814</v>
+      </c>
       <c r="H8" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
+      <c r="I8" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J8" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K8" s="21">
         <f t="shared" ref="K8:K27" si="0">I8-J8</f>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M8" s="21">
         <f>O8*12</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N8" s="27">
         <f>K8-M8</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O8" s="33">
         <f t="shared" ref="O8:O26" si="1">K8/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2518,7 +2535,9 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="D9" s="20" t="s">
         <v>68</v>
       </c>
@@ -2526,27 +2545,33 @@
       <c r="F9" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20">
+        <v>518912586</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
+      <c r="I9" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J9" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K9" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M9" s="21">
         <f t="shared" ref="M9:M26" si="3">O9*12</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N9" s="27">
         <f t="shared" ref="N9:N26" si="4">K9-M9</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O9" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3275,7 +3300,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>1264387.02</v>
+        <v>3937088.94</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3283,15 +3308,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>135470.03785714286</v>
+        <v>421830.95785714278</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>1128916.9821428573</v>
+        <v>3515257.9821428573</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>11289.169821428572</v>
+        <v>35152.579821428575</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3477,8 +3502,8 @@
       <c r="A36">
         <v>4</v>
       </c>
-      <c r="C36" s="19">
-        <v>46334</v>
+      <c r="C36" s="19" t="s">
+        <v>90</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>68</v>
@@ -3516,7 +3541,9 @@
       <c r="A37">
         <v>5</v>
       </c>
-      <c r="C37" s="19"/>
+      <c r="C37" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="D37" s="20" t="s">
         <v>68</v>
       </c>
@@ -3524,24 +3551,29 @@
       <c r="F37" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G37" s="37"/>
+      <c r="G37" s="37" t="s">
+        <v>91</v>
+      </c>
       <c r="H37" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
-      <c r="K37" s="21"/>
+      <c r="K37" s="21">
+        <f>11988+10656+179820</f>
+        <v>202464</v>
+      </c>
       <c r="M37" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21692.571428571428</v>
       </c>
       <c r="N37" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>180771.42857142858</v>
       </c>
       <c r="O37" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1807.7142857142858</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -3556,24 +3588,29 @@
       <c r="F38" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G38" s="37"/>
+      <c r="G38" s="37" t="s">
+        <v>89</v>
+      </c>
       <c r="H38" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I38" s="20"/>
       <c r="J38" s="20"/>
-      <c r="K38" s="21"/>
+      <c r="K38" s="21">
+        <f>11988+10656+179820</f>
+        <v>202464</v>
+      </c>
       <c r="M38" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21692.571428571428</v>
       </c>
       <c r="N38" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>180771.42857142858</v>
       </c>
       <c r="O38" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1807.7142857142858</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -4082,7 +4119,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>602280</v>
+        <v>1007208</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4090,15 +4127,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>64530</v>
+        <v>107915.14285714284</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>537750</v>
+        <v>899292.85714285728</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>5377.5</v>
+        <v>8992.9285714285725</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD115620-76C9-43AC-A518-7928CD15E53F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5023BB-D194-46FA-A7B3-45647A9B3C32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="94">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -309,6 +309,12 @@
   </si>
   <si>
     <t>R06</t>
+  </si>
+  <si>
+    <t>R08</t>
+  </si>
+  <si>
+    <t>08/18/2026</t>
   </si>
 </sst>
 </file>
@@ -2583,7 +2589,9 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
+      <c r="C10" s="19" t="s">
+        <v>93</v>
+      </c>
       <c r="D10" s="20" t="s">
         <v>68</v>
       </c>
@@ -2591,27 +2599,33 @@
       <c r="F10" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="20">
+        <v>518918403</v>
+      </c>
       <c r="H10" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="I10" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J10" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K10" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M10" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N10" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O10" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -3300,7 +3314,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>3937088.94</v>
+        <v>5273439.9000000004</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3308,15 +3322,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>421830.95785714278</v>
+        <v>565011.41785714275</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>3515257.9821428573</v>
+        <v>4708428.4821428573</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>35152.579821428575</v>
+        <v>47084.284821428577</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3502,8 +3516,8 @@
       <c r="A36">
         <v>4</v>
       </c>
-      <c r="C36" s="19" t="s">
-        <v>90</v>
+      <c r="C36" s="19">
+        <v>46334</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>68</v>
@@ -3580,7 +3594,9 @@
       <c r="A38">
         <v>6</v>
       </c>
-      <c r="C38" s="19"/>
+      <c r="C38" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="D38" s="20" t="s">
         <v>68</v>
       </c>
@@ -3617,7 +3633,9 @@
       <c r="A39">
         <v>7</v>
       </c>
-      <c r="C39" s="19"/>
+      <c r="C39" s="19" t="s">
+        <v>93</v>
+      </c>
       <c r="D39" s="20" t="s">
         <v>68</v>
       </c>
@@ -3625,24 +3643,29 @@
       <c r="F39" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="37"/>
+      <c r="G39" s="37" t="s">
+        <v>92</v>
+      </c>
       <c r="H39" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
-      <c r="K39" s="21"/>
+      <c r="K39" s="21">
+        <f>11988+191808</f>
+        <v>203796</v>
+      </c>
       <c r="M39" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N39" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O39" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -4119,7 +4142,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>1007208</v>
+        <v>1211004</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4127,15 +4150,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>107915.14285714284</v>
+        <v>129750.42857142855</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>899292.85714285728</v>
+        <v>1081253.5714285716</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>8992.9285714285725</v>
+        <v>10812.535714285716</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5023BB-D194-46FA-A7B3-45647A9B3C32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF19D2FC-5546-414E-BD53-2423DDC6DC12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="98">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -315,6 +315,18 @@
   </si>
   <si>
     <t>08/18/2026</t>
+  </si>
+  <si>
+    <t>18/19/2026</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>08/19/2026</t>
+  </si>
+  <si>
+    <t>R09</t>
   </si>
 </sst>
 </file>
@@ -2637,7 +2649,9 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="C11" s="19"/>
+      <c r="C11" s="19" t="s">
+        <v>96</v>
+      </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
       </c>
@@ -2645,27 +2659,33 @@
       <c r="F11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="20">
+        <v>518921976</v>
+      </c>
       <c r="H11" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
+      <c r="I11" s="21">
+        <v>1356048</v>
+      </c>
+      <c r="J11" s="21">
+        <v>58168.62</v>
+      </c>
       <c r="K11" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1297879.3799999999</v>
       </c>
       <c r="M11" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>139058.505</v>
       </c>
       <c r="N11" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1158820.875</v>
       </c>
       <c r="O11" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11588.20875</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2677,7 +2697,9 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>96</v>
+      </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
       </c>
@@ -2685,27 +2707,33 @@
       <c r="F12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20">
+        <v>518921567</v>
+      </c>
       <c r="H12" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
+      <c r="I12" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J12" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K12" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M12" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N12" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O12" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -3314,7 +3342,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>5273439.9000000004</v>
+        <v>7907670.2400000002</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3322,15 +3350,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>565011.41785714275</v>
+        <v>847250.38285714271</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>4708428.4821428573</v>
+        <v>7060419.8571428573</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>47084.284821428577</v>
+        <v>70604.198571428569</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3672,7 +3700,9 @@
       <c r="A40">
         <v>8</v>
       </c>
-      <c r="C40" s="19"/>
+      <c r="C40" s="19" t="s">
+        <v>94</v>
+      </c>
       <c r="D40" s="20" t="s">
         <v>68</v>
       </c>
@@ -3680,31 +3710,38 @@
       <c r="F40" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G40" s="37"/>
+      <c r="G40" s="37" t="s">
+        <v>97</v>
+      </c>
       <c r="H40" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
-      <c r="K40" s="21"/>
+      <c r="K40" s="21">
+        <f>11988+10656+179820</f>
+        <v>202464</v>
+      </c>
       <c r="M40" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21692.571428571428</v>
       </c>
       <c r="N40" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>180771.42857142858</v>
       </c>
       <c r="O40" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1807.7142857142858</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9</v>
       </c>
-      <c r="C41" s="19"/>
+      <c r="C41" s="19" t="s">
+        <v>94</v>
+      </c>
       <c r="D41" s="20" t="s">
         <v>68</v>
       </c>
@@ -3712,24 +3749,29 @@
       <c r="F41" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G41" s="37"/>
+      <c r="G41" s="37" t="s">
+        <v>95</v>
+      </c>
       <c r="H41" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
-      <c r="K41" s="21"/>
+      <c r="K41" s="21">
+        <f>11988+143856</f>
+        <v>155844</v>
+      </c>
       <c r="M41" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16697.571428571428</v>
       </c>
       <c r="N41" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>139146.42857142858</v>
       </c>
       <c r="O41" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1391.4642857142858</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -4142,7 +4184,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>1211004</v>
+        <v>1569312</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4150,15 +4192,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>129750.42857142855</v>
+        <v>168140.57142857139</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1081253.5714285716</v>
+        <v>1401171.4285714289</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>10812.535714285716</v>
+        <v>14011.714285714288</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4265,7 +4307,9 @@
       <c r="A61">
         <v>2</v>
       </c>
-      <c r="C61" s="19"/>
+      <c r="C61" s="19" t="s">
+        <v>96</v>
+      </c>
       <c r="D61" s="20" t="s">
         <v>68</v>
       </c>
@@ -4274,25 +4318,28 @@
         <v>70</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H61" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I61" s="20"/>
       <c r="J61" s="20"/>
-      <c r="K61" s="21"/>
+      <c r="K61" s="21">
+        <f>11232+11340</f>
+        <v>22572</v>
+      </c>
       <c r="M61" s="21">
         <f t="shared" ref="M61:M80" si="11">O61*12</f>
-        <v>0</v>
+        <v>2418.4285714285716</v>
       </c>
       <c r="N61" s="27">
         <f>K61-M61</f>
-        <v>0</v>
+        <v>20153.571428571428</v>
       </c>
       <c r="O61" s="33">
         <f t="shared" ref="O61:O80" si="12">K61/112</f>
-        <v>0</v>
+        <v>201.53571428571428</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -4929,7 +4976,7 @@
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
-        <v>0</v>
+        <v>22572</v>
       </c>
       <c r="L82" s="44">
         <f ca="1">SUM(L61:L85)</f>
@@ -4937,15 +4984,15 @@
       </c>
       <c r="M82" s="44">
         <f>SUM(M61:M81)</f>
-        <v>0</v>
+        <v>2418.4285714285716</v>
       </c>
       <c r="N82" s="44">
         <f>SUM(N61:N81)</f>
-        <v>0</v>
+        <v>20153.571428571428</v>
       </c>
       <c r="O82" s="45">
         <f>SUM(O61:O81)</f>
-        <v>0</v>
+        <v>201.53571428571428</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF19D2FC-5546-414E-BD53-2423DDC6DC12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BF8414-A1E7-42B1-A4DB-B9DFB362CD95}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BF8414-A1E7-42B1-A4DB-B9DFB362CD95}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DD74A1-4DFB-4869-A93E-08BE172FE9D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="99">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -317,9 +317,6 @@
     <t>08/18/2026</t>
   </si>
   <si>
-    <t>18/19/2026</t>
-  </si>
-  <si>
     <t>R10</t>
   </si>
   <si>
@@ -327,6 +324,12 @@
   </si>
   <si>
     <t>R09</t>
+  </si>
+  <si>
+    <t>08/24/2026</t>
+  </si>
+  <si>
+    <t>R11</t>
   </si>
 </sst>
 </file>
@@ -2650,7 +2653,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
@@ -2698,7 +2701,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
@@ -2745,7 +2748,9 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="19" t="s">
+        <v>97</v>
+      </c>
       <c r="D13" s="20" t="s">
         <v>68</v>
       </c>
@@ -2753,27 +2758,33 @@
       <c r="F13" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20">
+        <v>518933761</v>
+      </c>
       <c r="H13" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="I13" s="21">
+        <v>1299728</v>
+      </c>
+      <c r="J13" s="21">
+        <v>87768.13</v>
+      </c>
       <c r="K13" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1211959.8700000001</v>
       </c>
       <c r="M13" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>129852.84321428572</v>
       </c>
       <c r="N13" s="27">
         <f>K13-M13</f>
-        <v>0</v>
+        <v>1082107.0267857143</v>
       </c>
       <c r="O13" s="33">
         <f>K13/112</f>
-        <v>0</v>
+        <v>10821.070267857143</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -2785,7 +2796,9 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>97</v>
+      </c>
       <c r="D14" s="20" t="s">
         <v>68</v>
       </c>
@@ -2793,27 +2806,33 @@
       <c r="F14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="20">
+        <v>518934094</v>
+      </c>
       <c r="H14" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
+      <c r="I14" s="36">
+        <v>1397196</v>
+      </c>
+      <c r="J14" s="36">
+        <v>60845.04</v>
+      </c>
       <c r="K14" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M14" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N14" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O14" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -3342,7 +3361,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>7907670.2400000002</v>
+        <v>10455981.07</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3350,15 +3369,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>847250.38285714271</v>
+        <v>1120283.6860714285</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>7060419.8571428573</v>
+        <v>9335697.3839285709</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>70604.198571428569</v>
+        <v>93356.973839285711</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3701,7 +3720,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>68</v>
@@ -3711,7 +3730,7 @@
         <v>70</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H40" s="20" t="s">
         <v>85</v>
@@ -3740,7 +3759,7 @@
         <v>9</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>68</v>
@@ -3750,7 +3769,7 @@
         <v>70</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H41" s="20" t="s">
         <v>85</v>
@@ -3778,7 +3797,9 @@
       <c r="A42">
         <v>10</v>
       </c>
-      <c r="C42" s="19"/>
+      <c r="C42" s="19" t="s">
+        <v>97</v>
+      </c>
       <c r="D42" s="20" t="s">
         <v>68</v>
       </c>
@@ -3786,24 +3807,29 @@
       <c r="F42" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G42" s="37"/>
+      <c r="G42" s="37" t="s">
+        <v>98</v>
+      </c>
       <c r="H42" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I42" s="20"/>
       <c r="J42" s="20"/>
-      <c r="K42" s="21"/>
+      <c r="K42" s="21">
+        <f>23976+179820+2268</f>
+        <v>206064</v>
+      </c>
       <c r="M42" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22078.285714285714</v>
       </c>
       <c r="N42" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>183985.71428571429</v>
       </c>
       <c r="O42" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1839.8571428571429</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -4184,7 +4210,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>1569312</v>
+        <v>1775376</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4192,15 +4218,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>168140.57142857139</v>
+        <v>190218.8571428571</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1401171.4285714289</v>
+        <v>1585157.1428571432</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>14011.714285714288</v>
+        <v>15851.571428571431</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4308,7 +4334,7 @@
         <v>2</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D61" s="20" t="s">
         <v>68</v>
@@ -4318,7 +4344,7 @@
         <v>70</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H61" s="20" t="s">
         <v>85</v>

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DD74A1-4DFB-4869-A93E-08BE172FE9D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DA2BDC-4E3F-42CD-A016-DB5A23DC49FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="103">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -330,6 +330,18 @@
   </si>
   <si>
     <t>R11</t>
+  </si>
+  <si>
+    <t>08/25/2026</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>08/26/2026</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +2856,9 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="D15" s="20" t="s">
         <v>68</v>
       </c>
@@ -2852,27 +2866,33 @@
       <c r="F15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="20">
+        <v>518937767</v>
+      </c>
       <c r="H15" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="I15" s="21">
+        <v>1341688</v>
+      </c>
+      <c r="J15" s="21">
+        <v>57421.279999999999</v>
+      </c>
       <c r="K15" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1284266.72</v>
       </c>
       <c r="M15" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>137600.00571428571</v>
       </c>
       <c r="N15" s="27">
         <f>K15-M15</f>
-        <v>0</v>
+        <v>1146666.7142857143</v>
       </c>
       <c r="O15" s="33">
         <f>K15/112</f>
-        <v>0</v>
+        <v>11466.667142857143</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -2884,7 +2904,9 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="D16" s="20" t="s">
         <v>68</v>
       </c>
@@ -2892,27 +2914,33 @@
       <c r="F16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="20">
+        <v>518938287</v>
+      </c>
       <c r="H16" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
+      <c r="I16" s="21">
+        <v>1414821</v>
+      </c>
+      <c r="J16" s="21">
+        <v>61338.39</v>
+      </c>
       <c r="K16" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1353482.61</v>
       </c>
       <c r="M16" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>145015.99392857144</v>
       </c>
       <c r="N16" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1208466.6160714286</v>
       </c>
       <c r="O16" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12084.666160714287</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -2924,7 +2952,9 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="C17" s="19"/>
+      <c r="C17" s="19" t="s">
+        <v>102</v>
+      </c>
       <c r="D17" s="20" t="s">
         <v>68</v>
       </c>
@@ -2932,27 +2962,33 @@
       <c r="F17" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="20">
+        <v>518942028</v>
+      </c>
       <c r="H17" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
+      <c r="I17" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J17" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K17" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M17" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N17" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O17" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -3361,7 +3397,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>10455981.07</v>
+        <v>14430081.359999999</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3369,15 +3405,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>1120283.6860714285</v>
+        <v>1546080.1457142856</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>9335697.3839285709</v>
+        <v>12884001.214285715</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>93356.973839285711</v>
+        <v>128840.01214285714</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3836,7 +3872,9 @@
       <c r="A43">
         <v>11</v>
       </c>
-      <c r="C43" s="19"/>
+      <c r="C43" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="D43" s="20" t="s">
         <v>68</v>
       </c>
@@ -3844,31 +3882,38 @@
       <c r="F43" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G43" s="37"/>
+      <c r="G43" s="37" t="s">
+        <v>100</v>
+      </c>
       <c r="H43" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I43" s="20"/>
       <c r="J43" s="20"/>
-      <c r="K43" s="21"/>
+      <c r="K43" s="21">
+        <f>11988+119880+5292+6048+36288</f>
+        <v>179496</v>
+      </c>
       <c r="M43" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19231.714285714286</v>
       </c>
       <c r="N43" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>160264.28571428571</v>
       </c>
       <c r="O43" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1602.6428571428571</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>12</v>
       </c>
-      <c r="C44" s="19"/>
+      <c r="C44" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="D44" s="20" t="s">
         <v>68</v>
       </c>
@@ -3876,24 +3921,29 @@
       <c r="F44" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G44" s="37"/>
+      <c r="G44" s="37" t="s">
+        <v>101</v>
+      </c>
       <c r="H44" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I44" s="20"/>
       <c r="J44" s="20"/>
-      <c r="K44" s="21"/>
+      <c r="K44" s="21">
+        <f>7560+15120+59940+9072</f>
+        <v>91692</v>
+      </c>
       <c r="M44" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9824.1428571428569</v>
       </c>
       <c r="N44" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>81867.857142857145</v>
       </c>
       <c r="O44" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>818.67857142857144</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -4210,7 +4260,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>1775376</v>
+        <v>2046564</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4218,15 +4268,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>190218.8571428571</v>
+        <v>219274.71428571426</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1585157.1428571432</v>
+        <v>1827289.2857142859</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>15851.571428571431</v>
+        <v>18272.892857142862</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DA2BDC-4E3F-42CD-A016-DB5A23DC49FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A131C716-99C9-4092-A9F2-B8954F66C569}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="106">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -342,6 +342,15 @@
   </si>
   <si>
     <t>08/26/2026</t>
+  </si>
+  <si>
+    <t>08/28/2026</t>
+  </si>
+  <si>
+    <t>08/27/2026</t>
+  </si>
+  <si>
+    <t>R14</t>
   </si>
 </sst>
 </file>
@@ -3000,7 +3009,9 @@
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="19" t="s">
+        <v>103</v>
+      </c>
       <c r="D18" s="20" t="s">
         <v>68</v>
       </c>
@@ -3008,27 +3019,33 @@
       <c r="F18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="20">
+        <v>518945451</v>
+      </c>
       <c r="H18" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
+      <c r="I18" s="21">
+        <v>1345788</v>
+      </c>
+      <c r="J18" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K18" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1284942.96</v>
       </c>
       <c r="M18" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>137672.46</v>
       </c>
       <c r="N18" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1147270.5</v>
       </c>
       <c r="O18" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11472.705</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -3040,7 +3057,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>104</v>
+      </c>
       <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
@@ -3048,27 +3067,33 @@
       <c r="F19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="20"/>
+      <c r="G19" s="20">
+        <v>518945971</v>
+      </c>
       <c r="H19" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
+      <c r="I19" s="21">
+        <v>1381428</v>
+      </c>
+      <c r="J19" s="21">
+        <v>58708.08</v>
+      </c>
       <c r="K19" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1322719.92</v>
       </c>
       <c r="M19" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>141719.9914285714</v>
       </c>
       <c r="N19" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1180999.9285714286</v>
       </c>
       <c r="O19" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11809.999285714284</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -3397,7 +3422,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>14430081.359999999</v>
+        <v>17037744.240000002</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3405,15 +3430,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>1546080.1457142856</v>
+        <v>1825472.597142857</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>12884001.214285715</v>
+        <v>15212271.642857144</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>128840.01214285714</v>
+        <v>152122.71642857144</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3950,7 +3975,9 @@
       <c r="A45">
         <v>13</v>
       </c>
-      <c r="C45" s="19"/>
+      <c r="C45" s="19" t="s">
+        <v>104</v>
+      </c>
       <c r="D45" s="20" t="s">
         <v>68</v>
       </c>
@@ -3958,24 +3985,29 @@
       <c r="F45" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G45" s="37"/>
+      <c r="G45" s="37" t="s">
+        <v>105</v>
+      </c>
       <c r="H45" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I45" s="20"/>
       <c r="J45" s="20"/>
-      <c r="K45" s="21"/>
+      <c r="K45" s="21">
+        <f>35964+143856+9072+8064</f>
+        <v>196956</v>
+      </c>
       <c r="M45" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21102.428571428572</v>
       </c>
       <c r="N45" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>175853.57142857142</v>
       </c>
       <c r="O45" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1758.5357142857142</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -4260,7 +4292,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>2046564</v>
+        <v>2243520</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4268,15 +4300,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>219274.71428571426</v>
+        <v>240377.14285714284</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1827289.2857142859</v>
+        <v>2003142.8571428573</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>18272.892857142862</v>
+        <v>20031.428571428576</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A131C716-99C9-4092-A9F2-B8954F66C569}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFD3BF0-31A8-412F-A279-BBE3407FE486}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="107">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>R14</t>
+  </si>
+  <si>
+    <t>R16</t>
   </si>
 </sst>
 </file>
@@ -4014,7 +4017,9 @@
       <c r="A46">
         <v>14</v>
       </c>
-      <c r="C46" s="19"/>
+      <c r="C46" s="19" t="s">
+        <v>103</v>
+      </c>
       <c r="D46" s="20" t="s">
         <v>68</v>
       </c>
@@ -4022,24 +4027,29 @@
       <c r="F46" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G46" s="37"/>
+      <c r="G46" s="37" t="s">
+        <v>106</v>
+      </c>
       <c r="H46" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I46" s="20"/>
       <c r="J46" s="20"/>
-      <c r="K46" s="21"/>
+      <c r="K46" s="21">
+        <f>23976+179820</f>
+        <v>203796</v>
+      </c>
       <c r="M46" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N46" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O46" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -4292,7 +4302,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>2243520</v>
+        <v>2447316</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4300,15 +4310,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>240377.14285714284</v>
+        <v>262212.42857142858</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>2003142.8571428573</v>
+        <v>2185103.5714285714</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>20031.428571428576</v>
+        <v>21851.035714285717</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/PURCHASES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFD3BF0-31A8-412F-A279-BBE3407FE486}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C580E3-46D4-4FBE-BDE9-F6D8ED099382}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="109">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>R16</t>
+  </si>
+  <si>
+    <t>08/29/2026</t>
+  </si>
+  <si>
+    <t>R17</t>
   </si>
 </sst>
 </file>
@@ -4056,7 +4062,9 @@
       <c r="A47">
         <v>15</v>
       </c>
-      <c r="C47" s="19"/>
+      <c r="C47" s="19" t="s">
+        <v>107</v>
+      </c>
       <c r="D47" s="20" t="s">
         <v>68</v>
       </c>
@@ -4064,24 +4072,29 @@
       <c r="F47" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="37"/>
+      <c r="G47" s="37" t="s">
+        <v>108</v>
+      </c>
       <c r="H47" s="20" t="s">
         <v>85</v>
       </c>
       <c r="I47" s="20"/>
       <c r="J47" s="20"/>
-      <c r="K47" s="21"/>
+      <c r="K47" s="21">
+        <f>7560+23976+155844+9072</f>
+        <v>196452</v>
+      </c>
       <c r="M47" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21048.428571428572</v>
       </c>
       <c r="N47" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>175403.57142857142</v>
       </c>
       <c r="O47" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1754.0357142857142</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -4302,7 +4315,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>2447316</v>
+        <v>2643768</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4310,15 +4323,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>262212.42857142858</v>
+        <v>283260.85714285716</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>2185103.5714285714</v>
+        <v>2360507.1428571427</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>21851.035714285717</v>
+        <v>23605.071428571431</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
